--- a/artfynd/A 53293-2021 artfynd.xlsx
+++ b/artfynd/A 53293-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53293-2021 artfynd.xlsx
+++ b/artfynd/A 53293-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98626924</v>
+        <v>98626926</v>
       </c>
       <c r="B2" t="n">
-        <v>93158</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2818</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -717,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554658.7404603108</v>
+        <v>554659</v>
       </c>
       <c r="R2" t="n">
-        <v>6365739.935462777</v>
+        <v>6365740</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,19 +745,9 @@
           <t>2022-02-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-02-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,15 +774,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98627352</v>
+        <v>98626518</v>
       </c>
       <c r="B3" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,35 +785,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6439</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554708.047038834</v>
+        <v>554870</v>
       </c>
       <c r="R3" t="n">
-        <v>6365683.5253448</v>
+        <v>6365735</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -863,19 +844,9 @@
           <t>2022-02-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-02-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,52 +873,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98626926</v>
+        <v>98570775</v>
       </c>
       <c r="B4" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81025</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>738</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>554658.7404603108</v>
+        <v>554859</v>
       </c>
       <c r="R4" t="n">
-        <v>6365739.935462777</v>
+        <v>6365683</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,22 +939,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-02-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-02-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,57 +971,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>99019459</v>
+        <v>98571319</v>
       </c>
       <c r="B5" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81025</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>738</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>554742.9972100354</v>
+        <v>554874</v>
       </c>
       <c r="R5" t="n">
-        <v>6365692.070009939</v>
+        <v>6365691</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1093,22 +1037,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-03-10</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-03-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,57 +1069,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>99019064</v>
+        <v>98576459</v>
       </c>
       <c r="B6" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81025</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>738</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>554693.9426956236</v>
+        <v>554893</v>
       </c>
       <c r="R6" t="n">
-        <v>6365729.639013576</v>
+        <v>6365645</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,27 +1135,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-03-10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-03-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Sångläte</t>
+          <t>2022-02-11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,52 +1167,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>98570836</v>
+        <v>98628327</v>
       </c>
       <c r="B7" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81025</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>738</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>554858.0183082543</v>
+        <v>554866</v>
       </c>
       <c r="R7" t="n">
-        <v>6365683.384494441</v>
+        <v>6365647</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1331,22 +1233,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-02-11</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-02-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1373,52 +1265,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>98570512</v>
+        <v>99018336</v>
       </c>
       <c r="B8" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81025</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>738</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>554892.5410791121</v>
+        <v>554889</v>
       </c>
       <c r="R8" t="n">
-        <v>6365723.690538089</v>
+        <v>6365663</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1445,22 +1331,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-02-11</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-02-11</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,19 +1363,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>98576459</v>
+        <v>99018521</v>
       </c>
       <c r="B9" t="n">
-        <v>79136</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81025</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1528,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>554892.5265104687</v>
+        <v>554887</v>
       </c>
       <c r="R9" t="n">
-        <v>6365644.544506027</v>
+        <v>6365641</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1558,22 +1429,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-02-11</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-02-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,15 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>98570775</v>
+        <v>98628293</v>
       </c>
       <c r="B10" t="n">
-        <v>79136</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83313</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>738</v>
+        <v>1468</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Brunskaftad blekspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Sclerophora farinacea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(Chevall.) Chevall.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1641,10 +1497,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>554858.0183082543</v>
+        <v>554866</v>
       </c>
       <c r="R10" t="n">
-        <v>6365683.384494441</v>
+        <v>6365647</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1671,22 +1527,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-02-11</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-02-11</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,15 +1559,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>98570802</v>
+        <v>98627454</v>
       </c>
       <c r="B11" t="n">
-        <v>92939</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,21 +1570,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2779</v>
+        <v>2590</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1755,10 +1596,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>554858.0183082543</v>
+        <v>554794</v>
       </c>
       <c r="R11" t="n">
-        <v>6365683.384494441</v>
+        <v>6365672</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1785,22 +1626,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-02-11</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-02-11</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,51 +1658,47 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>98571319</v>
+        <v>98570802</v>
       </c>
       <c r="B12" t="n">
-        <v>79136</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>738</v>
+        <v>2779</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>554873.0118704739</v>
+        <v>554859</v>
       </c>
       <c r="R12" t="n">
-        <v>6365691.662124768</v>
+        <v>6365683</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1901,19 +1728,9 @@
           <t>2022-02-11</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-02-11</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,51 +1757,47 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>98628327</v>
+        <v>98628355</v>
       </c>
       <c r="B13" t="n">
-        <v>79136</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>738</v>
+        <v>2779</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>554865.5147831375</v>
+        <v>554880</v>
       </c>
       <c r="R13" t="n">
-        <v>6365647.411821015</v>
+        <v>6365684</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2014,19 +1827,9 @@
           <t>2022-02-15</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-02-15</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2053,15 +1856,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>98627460</v>
+        <v>99018515</v>
       </c>
       <c r="B14" t="n">
-        <v>93158</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,21 +1867,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2818</v>
+        <v>2779</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2095,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>554794.5037649963</v>
+        <v>554863</v>
       </c>
       <c r="R14" t="n">
-        <v>6365672.84005369</v>
+        <v>6365654</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2125,22 +1923,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-02-15</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-02-15</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2167,51 +1955,47 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>98628293</v>
+        <v>99019708</v>
       </c>
       <c r="B15" t="n">
-        <v>73699</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1468</v>
+        <v>2779</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brunskaftad blekspik</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sclerophora farinacea</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Chevall.) Chevall.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hultsfred, Sm</t>
+          <t>Ekenäs 4, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>554865.5147831375</v>
+        <v>554935</v>
       </c>
       <c r="R15" t="n">
-        <v>6365647.411821015</v>
+        <v>6365584</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2238,22 +2022,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-02-15</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-02-15</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,15 +2054,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>98626518</v>
+        <v>99019758</v>
       </c>
       <c r="B16" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2296,21 +2065,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>210</v>
+        <v>2779</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2318,14 +2087,14 @@
       <c r="L16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hultsfred, Sm</t>
+          <t>Ekenäs 4, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>554869.7289388217</v>
+        <v>554927</v>
       </c>
       <c r="R16" t="n">
-        <v>6365735.228644441</v>
+        <v>6365613</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2352,22 +2121,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-02-15</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-02-15</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2394,15 +2153,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>98627454</v>
+        <v>98626924</v>
       </c>
       <c r="B17" t="n">
-        <v>94160</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,21 +2164,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2590</v>
+        <v>2818</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2436,10 +2190,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>554794.5037649963</v>
+        <v>554659</v>
       </c>
       <c r="R17" t="n">
-        <v>6365672.84005369</v>
+        <v>6365740</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2469,19 +2223,9 @@
           <t>2022-02-15</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-02-15</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2508,15 +2252,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>98628355</v>
+        <v>98627460</v>
       </c>
       <c r="B18" t="n">
-        <v>92939</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,21 +2263,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2779</v>
+        <v>2818</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2550,10 +2289,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>554880.1321132497</v>
+        <v>554794</v>
       </c>
       <c r="R18" t="n">
-        <v>6365683.681751701</v>
+        <v>6365672</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2583,19 +2322,9 @@
           <t>2022-02-15</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-02-15</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2622,15 +2351,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>98628227</v>
+        <v>98627352</v>
       </c>
       <c r="B19" t="n">
-        <v>78448</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2638,21 +2362,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6003719</v>
+        <v>6439</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Traslav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scytinium lichenoides</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2663,10 +2387,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>554867.7663124859</v>
+        <v>554709</v>
       </c>
       <c r="R19" t="n">
-        <v>6365640.442725862</v>
+        <v>6365684</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2696,19 +2420,9 @@
           <t>2022-02-15</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-02-15</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2735,51 +2449,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>99018521</v>
+        <v>99019843</v>
       </c>
       <c r="B20" t="n">
-        <v>79136</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44177</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>738</v>
+        <v>101735</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>554887.7228833435</v>
+        <v>554921</v>
       </c>
       <c r="R20" t="n">
-        <v>6365640.711023646</v>
+        <v>6365643</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2809,19 +2520,14 @@
           <t>2022-03-10</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-03-10</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2848,52 +2554,52 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>99018515</v>
+        <v>99018300</v>
       </c>
       <c r="B21" t="n">
-        <v>92939</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2779</v>
+        <v>103020</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>554862.7238963279</v>
+        <v>554888</v>
       </c>
       <c r="R21" t="n">
-        <v>6365654.373656064</v>
+        <v>6365702</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2923,19 +2629,14 @@
           <t>2022-03-10</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-03-10</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Sångläte</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2962,51 +2663,52 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>99018336</v>
+        <v>99019516</v>
       </c>
       <c r="B22" t="n">
-        <v>79136</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>738</v>
+        <v>103020</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>554889.5835618386</v>
+        <v>554757</v>
       </c>
       <c r="R22" t="n">
-        <v>6365662.810906362</v>
+        <v>6365670</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3036,19 +2738,14 @@
           <t>2022-03-10</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-03-10</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Sångläte</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3075,52 +2772,52 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>99019758</v>
+        <v>99019064</v>
       </c>
       <c r="B23" t="n">
-        <v>92939</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2779</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ekenäs 4, Hultsfred, Sm</t>
+          <t>Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>554926.9339569556</v>
+        <v>554693</v>
       </c>
       <c r="R23" t="n">
-        <v>6365613.240902229</v>
+        <v>6365730</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3150,19 +2847,14 @@
           <t>2022-03-10</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-03-10</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Sångläte</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3189,53 +2881,52 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>99019843</v>
+        <v>99019459</v>
       </c>
       <c r="B24" t="n">
-        <v>43464</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>101735</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>554920.5952839815</v>
+        <v>554744</v>
       </c>
       <c r="R24" t="n">
-        <v>6365643.306826354</v>
+        <v>6365692</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3265,24 +2956,9 @@
           <t>2022-03-10</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-03-10</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3309,57 +2985,47 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>99019516</v>
+        <v>98570512</v>
       </c>
       <c r="B25" t="n">
-        <v>56538</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103020</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>554757.3310819375</v>
+        <v>554893</v>
       </c>
       <c r="R25" t="n">
-        <v>6365669.110773435</v>
+        <v>6365724</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3386,27 +3052,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-03-10</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-03-10</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Sångläte</t>
+          <t>2022-02-11</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3433,57 +3084,47 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>99018300</v>
+        <v>98570836</v>
       </c>
       <c r="B26" t="n">
-        <v>56538</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103020</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>554887.9836569631</v>
+        <v>554859</v>
       </c>
       <c r="R26" t="n">
-        <v>6365701.554717115</v>
+        <v>6365683</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3510,27 +3151,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-03-10</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-03-10</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Sångläte</t>
+          <t>2022-02-11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3554,6 +3180,302 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>98626424</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>554894</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6365752</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Målilla</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2022-02-15</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2022-02-15</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>98626603</v>
+      </c>
+      <c r="B28" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>554844</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6365770</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Målilla</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2022-02-15</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2022-02-15</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>98628227</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80357</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6003719</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Traslav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Scytinium lichenoides</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>554868</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6365640</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Målilla</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2022-02-15</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2022-02-15</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53293-2021 artfynd.xlsx
+++ b/artfynd/A 53293-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -771,6 +776,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98626926</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98626518</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98570775</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1066,6 +1086,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98571319</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1164,6 +1189,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98576459</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1262,6 +1292,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98628327</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1360,6 +1395,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99018336</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99018521</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1556,6 +1601,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98628293</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1655,6 +1705,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98627454</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1754,6 +1809,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98570802</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1853,6 +1913,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98628355</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1952,6 +2017,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99018515</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2051,6 +2121,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99019708</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2150,6 +2225,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99019758</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2249,6 +2329,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98626924</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2348,6 +2433,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98627460</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2446,6 +2536,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98627352</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2551,6 +2646,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99019843</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2660,6 +2760,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99018300</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2769,6 +2874,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99019516</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2878,6 +2988,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99019064</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2982,6 +3097,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99019459</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3081,6 +3201,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98570512</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3180,6 +3305,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98570836</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3279,6 +3409,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98626424</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3378,6 +3513,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98626603</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3476,8 +3616,43 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98628227</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>